--- a/outputs/may-2026-real-events/details/03-hangang-drone-light-show-2026/bundle/tables/safety-checklists.xlsx
+++ b/outputs/may-2026-real-events/details/03-hangang-drone-light-show-2026/bundle/tables/safety-checklists.xlsx
@@ -270,7 +270,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>/Volumes/data/Dev/korea-mice-safety-agent/outputs/may-2026-real-events/details/03-hangang-drone-light-show-2026</t>
+          <t>outputs/may-2026-real-events/details/03-hangang-drone-light-show-2026</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1953,42 +1953,42 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>사전</t>
+          <t>개장 전</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>D-1 18:00</t>
+          <t>개장 T-180</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>도로·교통통제 구역</t>
+          <t>게이트·대기열·주요 동선</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>교통통제 고지, 우회동선, 비상차량 접근로, 경찰/도로관리청 연락 기준 확인</t>
+          <t>게이트 처리량, 대기열 펜스, 우회동선, 안내표지, 혼잡 단계별 통제 기준 설치 확인</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>교통·대외협력 담당</t>
+          <t>구역장</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>통제 도면/고지 캡처/현장 사진</t>
+          <t>설치 사진/도면 체크</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>경찰/지자체/안전총괄</t>
+          <t>안전총괄/보안팀</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>개장 T-150</t>
+          <t>개장 T-180</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2010,27 +2010,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>통제구간·승하차장·주차장</t>
+          <t>무대 구조·상부장치</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>통제표지, 라바콘/펜스, 우회 안내판, 셔틀·택시·버스 승하차장, 비상차량 접근로 설치 확인</t>
+          <t>트러스·LED·스피커·조명 고정, 안전핀·와이어, 처짐·흔들림, 무대 하부·후면 출입통제 확인</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>교통·대외협력 담당</t>
+          <t>공연안전 담당</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>교통통제 도면/현장 사진</t>
+          <t>구조·리깅 체크 사진/출입통제 사진</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>경찰/도로관리청/안전총괄</t>
+          <t>무대감독/시설·전기/안전총괄</t>
         </is>
       </c>
     </row>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>개장 T-180</t>
+          <t>개장 T-150</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2052,27 +2052,27 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>게이트·대기열·주요 동선</t>
+          <t>소방·피난</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>게이트 처리량, 대기열 펜스, 우회동선, 안내표지, 혼잡 단계별 통제 기준 설치 확인</t>
+          <t>비상구, 피난통로, 소화전, 방화문, 소방차 진입로, 임시구조물 차단 여부 확인</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>구역장</t>
+          <t>시설·방재 담당</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>설치 사진/도면 체크</t>
+          <t>소방·피난 점검표/사진</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>안전총괄/보안팀</t>
+          <t>베뉴 방재실/소방서</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>개장 T-180</t>
+          <t>개장 T-120</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2094,27 +2094,27 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>무대 구조·상부장치</t>
+          <t>의료·AED</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>트러스·LED·스피커·조명 고정, 안전핀·와이어, 처짐·흔들림, 무대 하부·후면 출입통제 확인</t>
+          <t>AED 위치, 의무실, 응급처치자, 구급차 접근동선, 119 신고 기준, 이송병원 연락 확인</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>공연안전 담당</t>
+          <t>의료담당</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>구조·리깅 체크 사진/출입통제 사진</t>
+          <t>AED 점검표/연락망</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>무대감독/시설·전기/안전총괄</t>
+          <t>119/안전총괄</t>
         </is>
       </c>
     </row>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>개장 T-150</t>
+          <t>개장 T-120</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2136,27 +2136,27 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>소방·피난</t>
+          <t>설치·철거 작업구역</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>비상구, 피난통로, 소화전, 방화문, 소방차 진입로, 임시구조물 차단 여부 확인</t>
+          <t>작업 종료, 잔여 공구·케이블·고소작업 장비 철수, 관람객 동선과 작업구역 분리 확인</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>시설·방재 담당</t>
+          <t>작업책임자</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>소방·피난 점검표/사진</t>
+          <t>작업종료 확인서/현장 사진</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>베뉴 방재실/소방서</t>
+          <t>안전총괄/시설담당</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>개장 T-120</t>
+          <t>개장 T-60</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2178,27 +2178,27 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>의료·AED</t>
+          <t>객석·스탠딩 구역</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AED 위치, 의무실, 응급처치자, 구급차 접근동선, 119 신고 기준, 이송병원 연락 확인</t>
+          <t>스탠딩 펜스, 무대 전면 압박 완충, 피난통로, 보안·의료 전진배치, 피난안내 방송문 확인</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>의료담당</t>
+          <t>공연안전 담당</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>AED 점검표/연락망</t>
+          <t>객석 도면/펜스 사진/무전 체크</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>119/안전총괄</t>
+          <t>보안팀/의료팀/안전총괄</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>개장 T-120</t>
+          <t>개장 T-45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2220,39 +2220,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>설치·철거 작업구역</t>
+          <t>전체 스태프</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>작업 종료, 잔여 공구·케이블·고소작업 장비 철수, 관람객 동선과 작업구역 분리 확인</t>
+          <t>안전 브리핑, 구역별 보고선, 무전 채널, 대피/중지/재개 방송문, 미아·분실·민원 처리 기준 공유</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>작업책임자</t>
+          <t>안전총괄</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>작업종료 확인서/현장 사진</t>
+          <t>브리핑 참석명단/무전 체크</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>안전총괄/시설담당</t>
+          <t>운영총괄</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>개장 전</t>
+          <t>공연 직전</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>개장 T-60</t>
+          <t>공연 T-15</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2262,27 +2262,27 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>등록·CCTV·촬영</t>
+          <t>무대감독·운영본부</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>개인정보 고지, CCTV 안내판, 촬영 고지, 현장 단말 잠금, 접근권한, 접속기록 담당 확인</t>
+          <t>공연중지 기준, 아티스트/무대감독 중지 신호, 전원 차단, 비상방송, 관객 현 위치 대기·분산 문구 공유</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>개인정보보호책임자</t>
+          <t>무대감독</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>고지문/안내판 사진/권한 점검표</t>
+          <t>무대감독 체크/방송문 승인/무전 로그</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>운영총괄/보안책임자</t>
+          <t>운영총괄/안전총괄</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>개장 T-60</t>
+          <t>개장 T-15</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2304,39 +2304,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>객석·스탠딩 구역</t>
+          <t>운영본부</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>스탠딩 펜스, 무대 전면 압박 완충, 피난통로, 보안·의료 전진배치, 피난안내 방송문 확인</t>
+          <t>개장 승인 hold point: 소방·피난, 의료, 보안, 동선, 전기, 식음료, 작업구역 이상 없음 확인 후 개장</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>공연안전 담당</t>
+          <t>운영총괄</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>객석 도면/펜스 사진/무전 체크</t>
+          <t>개장 승인 체크/무전 로그</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>보안팀/의료팀/안전총괄</t>
+          <t>안전총괄</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>개장 전</t>
+          <t>운영 중</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>개장 T-45</t>
+          <t>30분 간격</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2346,39 +2346,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>전체 스태프</t>
+          <t>게이트·혼잡 구역</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>안전 브리핑, 구역별 보고선, 무전 채널, 대피/중지/재개 방송문, 미아·분실·민원 처리 기준 공유</t>
+          <t>구역별 체류 인원, 대기열 길이, 병목, 우회동선, 스태프 피로도, 위험 신고를 주기 보고</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>안전총괄</t>
+          <t>구역장</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>브리핑 참석명단/무전 체크</t>
+          <t>순찰 로그/사진</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>운영총괄</t>
+          <t>안전총괄/보안팀</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>공연 직전</t>
+          <t>운영 중</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>공연 T-15</t>
+          <t>60분 간격</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2388,39 +2388,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>무대감독·운영본부</t>
+          <t>옥외 구역</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>공연중지 기준, 아티스트/무대감독 중지 신호, 전원 차단, 비상방송, 관객 현 위치 대기·분산 문구 공유</t>
+          <t>기상, 강풍·우천·폭염, 임시구조물 흔들림, 전기 방수, 미끄럼 위험 확인</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>무대감독</t>
+          <t>시설·방재 담당</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>무대감독 체크/방송문 승인/무전 로그</t>
+          <t>기상 확인/현장 사진</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>운영총괄/안전총괄</t>
+          <t>운영총괄/지자체</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>개장 전</t>
+          <t>공연 중</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>개장 T-15</t>
+          <t>15분 간격</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2430,39 +2430,39 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>운영본부</t>
+          <t>무대 전면·스탠딩 구역</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>개장 승인 hold point: 소방·피난, 의료, 보안, 동선, 전기, 식음료, 작업구역 이상 없음 확인 후 개장</t>
+          <t>무대 전면 압박, 펜스 변형, 관객 쓰러짐, 역류, 응급환자, 구조물 흔들림, 전기 이상 징후 보고</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>운영총괄</t>
+          <t>공연안전 담당</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>개장 승인 체크/무전 로그</t>
+          <t>순찰 로그/현장 사진/의료·보안 출동 기록</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>안전총괄</t>
+          <t>무대감독/안전총괄/의료·보안</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>운영 중</t>
+          <t>야외·기상</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>30분 간격</t>
+          <t>상시</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2472,39 +2472,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>게이트·혼잡 구역</t>
+          <t>야외 무대·트러스</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>구역별 체류 인원, 대기열 길이, 병목, 우회동선, 스태프 피로도, 위험 신고를 주기 보고</t>
+          <t>강풍·우천·낙뢰, 무대 미끄럼, 전기 방수, 현수막·스크린 흔들림, 작업중지/공연중지 풍속 기준 확인</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>구역장</t>
+          <t>시설·방재 담당</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>순찰 로그/사진</t>
+          <t>기상 확인/중지 판단 기록/조치 사진</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>안전총괄/보안팀</t>
+          <t>운영총괄/지자체/소방</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>운영 중</t>
+          <t>피크</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>30분 간격</t>
+          <t>피크 T-30~T+30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2514,39 +2514,39 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>도로·교통통제 구역</t>
+          <t>주요 입퇴장 동선</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>보행자 대기열, 횡단보도 대기, 셔틀·주차장 진입 대기, 불법주정차, 응급차 접근 지연 여부 보고</t>
+          <t>혼잡 단계 상향 기준, 입장 속도 조절, 우회 안내, 의료·보안 전진 배치, 방송문 준비</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>교통·대외협력 담당</t>
+          <t>안전총괄</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>순찰 로그/사진/무전 기록</t>
+          <t>피크 점검 로그/방송 승인</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>경찰/도로관리청/안전총괄</t>
+          <t>운영총괄/경찰·소방</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>운영 중</t>
+          <t>폐장</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>60분 간격</t>
+          <t>폐장 T-30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2556,39 +2556,39 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>옥외 구역</t>
+          <t>퇴장 동선</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>기상, 강풍·우천·폭염, 임시구조물 흔들림, 전기 방수, 미끄럼 위험 확인</t>
+          <t>퇴장 분산 방송, 역/주차장/셔틀 대기열, 야간 조명, 우회동선, 미아·응급 잔여 이슈 확인</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>시설·방재 담당</t>
+          <t>구역장</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>기상 확인/현장 사진</t>
+          <t>폐장 전 점검표/방송 로그</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>운영총괄/지자체</t>
+          <t>안전총괄</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>공연 중</t>
+          <t>종료</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15분 간격</t>
+          <t>공연 종료 후</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>무대 전면·스탠딩 구역</t>
+          <t>퇴장·무대 구역</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>무대 전면 압박, 펜스 변형, 관객 쓰러짐, 역류, 응급환자, 구조물 흔들림, 전기 이상 징후 보고</t>
+          <t>퇴장 분산, 무대 접근통제, 전원 차단, 특수효과·화기 종료, 철거 전 관객 완전 분리 확인</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2613,24 +2613,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>순찰 로그/현장 사진/의료·보안 출동 기록</t>
+          <t>퇴장 로그/전원 차단 확인/철거 전 사진</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>무대감독/안전총괄/의료·보안</t>
+          <t>무대감독/안전총괄</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>야외·기상</t>
+          <t>폐장</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>상시</t>
+          <t>폐장 후 T+30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2640,39 +2640,39 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>야외 무대·트러스</t>
+          <t>운영본부</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>강풍·우천·낙뢰, 무대 미끄럼, 전기 방수, 현수막·스크린 흔들림, 작업중지/공연중지 풍속 기준 확인</t>
+          <t>사고·응급·민원·분실·미아 기록 취합, 미해결 조치 담당자 지정, 관계기관 종료 공유</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>시설·방재 담당</t>
+          <t>운영본부 기록담당</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>기상 확인/중지 판단 기록/조치 사진</t>
+          <t>일일 운영 종료 보고</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>운영총괄/지자체/소방</t>
+          <t>운영총괄</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>피크</t>
+          <t>철거</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>피크 T-30~T+30</t>
+          <t>철거 전</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2682,39 +2682,39 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>주요 입퇴장 동선</t>
+          <t>작업구역</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>혼잡 단계 상향 기준, 입장 속도 조절, 우회 안내, 의료·보안 전진 배치, 방송문 준비</t>
+          <t>관람객 완전 분리, 전기 차단/투입 승인, 작업허가, PPE, 추락·중량물·화기 작업 통제선 확인</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>안전총괄</t>
+          <t>작업책임자</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>피크 점검 로그/방송 승인</t>
+          <t>작업허가/교육명단/사진</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>운영총괄/경찰·소방</t>
+          <t>안전총괄/베뉴 담당</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>폐장</t>
+          <t>철거</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>폐장 T-30</t>
+          <t>철거 중</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2724,277 +2724,67 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>퇴장 동선</t>
+          <t>하역·반출 동선</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>퇴장 분산 방송, 역/주차장/셔틀 대기열, 야간 조명, 우회동선, 미아·응급 잔여 이슈 확인</t>
+          <t>지게차·하역장·차량 동선과 보행동선 분리, 하중분산, 잔재물 낙하·전도 위험 확인</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>구역장</t>
+          <t>하역책임자</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>폐장 전 점검표/방송 로그</t>
+          <t>하역 순찰 로그/사진</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>안전총괄</t>
+          <t>시설담당/안전총괄</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>폐장</t>
+          <t>종료</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>폐장 T+60</t>
+          <t>D+1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>도로·교통통제 구역</t>
+          <t>운영본부</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>통제물 철거, 원상복구, 노면 오염·파손, 민원·사고 기록, 통제 해제 관계기관 공유</t>
+          <t>사고보고서, 조치 전후 사진, 제출·승인 증빙, 개인정보 파기/보존, 베뉴 원상복구 확인 정리</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>교통·대외협력 담당</t>
+          <t>운영본부 기록담당</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>원상복구 사진/해제 공유 기록</t>
+          <t>종료 보고서/증빙철</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
-        <is>
-          <t>도로관리청/경찰/운영총괄</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>종료</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>공연 종료 후</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>퇴장·무대 구역</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>퇴장 분산, 무대 접근통제, 전원 차단, 특수효과·화기 종료, 철거 전 관객 완전 분리 확인</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>공연안전 담당</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>퇴장 로그/전원 차단 확인/철거 전 사진</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>무대감독/안전총괄</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>폐장</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>폐장 후 T+30</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>운영본부</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>사고·응급·민원·분실·미아 기록 취합, 미해결 조치 담당자 지정, 관계기관 종료 공유</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>운영본부 기록담당</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>일일 운영 종료 보고</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>운영총괄</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>철거</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>철거 전</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>작업구역</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>관람객 완전 분리, 전기 차단/투입 승인, 작업허가, PPE, 추락·중량물·화기 작업 통제선 확인</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>작업책임자</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>작업허가/교육명단/사진</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>안전총괄/베뉴 담당</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>철거</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>철거 중</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>하역·반출 동선</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>지게차·하역장·차량 동선과 보행동선 분리, 하중분산, 잔재물 낙하·전도 위험 확인</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>하역책임자</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>하역 순찰 로그/사진</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>시설담당/안전총괄</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>종료</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>D+1</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>운영본부</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>사고보고서, 조치 전후 사진, 제출·승인 증빙, 개인정보 파기/보존, 베뉴 원상복구 확인 정리</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>운영본부 기록담당</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>종료 보고서/증빙철</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
         <is>
           <t>운영총괄</t>
         </is>
@@ -3006,7 +2796,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3128,27 +2918,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>도로관리청/교통부서/경찰</t>
+          <t>옥외광고 담당부서/베뉴</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>도로점용허가, 교통소통대책, 도로공사 시행·착수·준공 서식</t>
+          <t>현수막·배너·안내판·전기 광고물 허가/신고</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>도로·보도·광장 점용, 차 없는 거리, 퍼레이드, 셔틀 승하차장, 임시시설 설치</t>
+          <t>옥외 임시 안내물, 지주형 표시물, 전광류 또는 전기 사용 광고물을 설치하는 경우</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>도로점용허가 신청 전, 설치·철거 착수 전, 종료 후 원상복구 시</t>
+          <t>표시·설치 전</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>도로법 시행령 별표 2, 도로법 시행규칙 별지 제11·12·13·33호서식</t>
+          <t>옥외광고물법 시행령 제5·7·12·14조와 관할 조례 확인</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3165,27 +2955,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>도로관리청/경찰/지자체 홍보 채널</t>
+          <t>관할 건축부서/베뉴 시설팀</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>통행금지·제한 또는 차량 운행 제한 공고</t>
+          <t>가설건축물 축조신고서, 피난안전 확인서, 임시사용승인 확인</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>일부 차로·보도·도로 통행 제한 또는 차량 운행 제한이 있는 경우</t>
+          <t>대형 텐트, 임시 전시장, 복층/다층 임시구조물, 공사 중 구역 임시 사용</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>통제 시행 전 사전 공고 및 현장 안내물 설치 전</t>
+          <t>설치 전 신고·승인, 개장 전 피난안전 확인</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>도로법 시행규칙 별지 제36호서식, 우회도로·문의처·비상차량 동선 포함</t>
+          <t>건축법 시행규칙 별지 제8·8의2·17호서식</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3202,27 +2992,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>옥외광고 담당부서/베뉴</t>
+          <t>소방서/베뉴 방재실/안전총괄</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>현수막·배너·안내판·전기 광고물 허가/신고</t>
+          <t>소방·피난 점검표, 화기·위험물 반입 승인, 임시소방시설 확인</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>옥외 임시 안내물, 지주형 표시물, 전광류 또는 전기 사용 광고물을 설치하는 경우</t>
+          <t>화기, 위험물, 임시전기, 부스·무대 설치, 피난통로 차단 위험이 있는 경우</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>표시·설치 전</t>
+          <t>설치 전, 개장 전, 피크 전, 철거 전</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>옥외광고물법 시행령 제5·7·12·14조와 관할 조례 확인</t>
+          <t>화재예방법·소방시설법 하위 별표와 베뉴 방재실 승인조건</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -3239,27 +3029,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>관할 건축부서/베뉴 시설팀</t>
+          <t>의료담당/AED 관리책임자/119·이송병원</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>가설건축물 축조신고서, 피난안전 확인서, 임시사용승인 확인</t>
+          <t>응급의료·AED·구급 이송 계획, AED 점검·교육·관리서류</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>대형 텐트, 임시 전시장, 복층/다층 임시구조물, 공사 중 구역 임시 사용</t>
+          <t>대규모 인파, 고령자/영유아/장애인, 스탠딩 공연, 야외·폭염·야간 행사</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>설치 전 신고·승인, 개장 전 피난안전 확인</t>
+          <t>개장 전, 운영 중, 사용/이송 발생 시</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>건축법 시행규칙 별지 제8·8의2·17호서식</t>
+          <t>응급의료법 AED 설치·관리, 시행규칙 구급차 장비·운행기록 기준</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3276,141 +3066,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>소방서/베뉴 방재실/안전총괄</t>
+          <t>시공/하역/전기 협력사/안전총괄</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>소방·피난 점검표, 화기·위험물 반입 승인, 임시소방시설 확인</t>
+          <t>설치·철거 작업자 안전계획서, 작업계획서, 교육명단, PPE·작업중지 기준</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>화기, 위험물, 임시전기, 부스·무대 설치, 피난통로 차단 위험이 있는 경우</t>
+          <t>부스·무대·트러스·전기·고소·중량물·화기·철거 작업이 있는 경우</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>설치 전, 개장 전, 피크 전, 철거 전</t>
+          <t>작업 전, 작업 중 변경 시, 철거 전</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>화재예방법·소방시설법 하위 별표와 베뉴 방재실 승인조건</t>
+          <t>산안법, 산안기준규칙 제38·42·321조, KOSHA Guide worker-safety layer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>개인정보 보호책임자/등록 대행사/보안 담당</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>개인정보 처리방침, 위탁계약, CCTV 안내, 접근권한·접속기록 점검</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>등록, QR/출입증, CCTV, 촬영, 앱 신고, VIP/초청자 명단 처리</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>수집 전 고지, 행사 전 위탁·보안점검, 종료 후 파기</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>개인정보보호법 제15·22·25·26·29·30조와 시행령 안전성 확보 조치</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>의료담당/AED 관리책임자/119·이송병원</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>응급의료·AED·구급 이송 계획, AED 점검·교육·관리서류</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>대규모 인파, 고령자/영유아/장애인, 스탠딩 공연, 야외·폭염·야간 행사</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>개장 전, 운영 중, 사용/이송 발생 시</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>응급의료법 AED 설치·관리, 시행규칙 구급차 장비·운행기록 기준</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>시공/하역/전기 협력사/안전총괄</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>설치·철거 작업자 안전계획서, 작업계획서, 교육명단, PPE·작업중지 기준</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>부스·무대·트러스·전기·고소·중량물·화기·철거 작업이 있는 경우</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>작업 전, 작업 중 변경 시, 철거 전</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>산안법, 산안기준규칙 제38·42·321조, KOSHA Guide worker-safety layer</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -4767,7 +4446,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>96</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4478,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>390</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4510,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>423</t>
         </is>
       </c>
     </row>
@@ -4863,7 +4542,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>421</t>
         </is>
       </c>
     </row>
@@ -4895,7 +4574,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>155</t>
         </is>
       </c>
     </row>
@@ -4927,7 +4606,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>482</t>
         </is>
       </c>
     </row>
@@ -4959,7 +4638,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>96</t>
         </is>
       </c>
     </row>
@@ -4991,7 +4670,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>583</t>
         </is>
       </c>
     </row>
@@ -5023,7 +4702,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>587</t>
         </is>
       </c>
     </row>
@@ -5055,7 +4734,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>595</t>
         </is>
       </c>
     </row>
@@ -5087,7 +4766,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>162</t>
         </is>
       </c>
     </row>
@@ -5119,7 +4798,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>636</t>
         </is>
       </c>
     </row>
@@ -5151,7 +4830,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>479</t>
         </is>
       </c>
     </row>
@@ -5183,7 +4862,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>97</t>
         </is>
       </c>
     </row>
@@ -5215,7 +4894,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>671</t>
         </is>
       </c>
     </row>
@@ -5247,7 +4926,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>837</t>
+          <t>704</t>
         </is>
       </c>
     </row>
@@ -5279,7 +4958,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>225</t>
         </is>
       </c>
     </row>
@@ -5311,7 +4990,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>731</t>
         </is>
       </c>
     </row>
@@ -5910,7 +5589,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6122,37 +5801,37 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>도로관리청/교통부서/경찰</t>
+          <t>옥외광고 담당부서/베뉴</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>도로점용허가, 교통소통대책, 도로공사 시행·착수·준공 서식</t>
+          <t>현수막·배너·안내판·전기 광고물 허가/신고</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>local_government | fire_police_medical</t>
+          <t>local_government | venue</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>T-14 협의 착수 / T-7 현장공고</t>
+          <t>T-7 설치·작업 전 승인</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-04-28 통제·우회 안내 확인</t>
+          <t>2026-05-04 개장 전 현장 확인</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>교통·대외협력 담당</t>
+          <t>시설·방재 담당</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -6162,17 +5841,17 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>도로관리청/경찰/지자체</t>
+          <t>소방서/베뉴 방재실/시설팀</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>운영본부/안내팀</t>
+          <t>운영본부/구역장</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>도로점용허가증/교통소통대책 승인/통제 공고 캡처</t>
+          <t>광고물 허가·신고필증/베뉴 설치 승인/설치 사진</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -6189,37 +5868,37 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>도로관리청/경찰/지자체 홍보 채널</t>
+          <t>관할 건축부서/베뉴 시설팀</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>통행금지·제한 또는 차량 운행 제한 공고</t>
+          <t>가설건축물 축조신고서, 피난안전 확인서, 임시사용승인 확인</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>local_government | fire_police_medical</t>
+          <t>local_government | venue | fire_police_medical</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>T-14 협의 착수 / T-7 현장공고</t>
+          <t>T-7 설치·작업 전 승인</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-04-28 통제·우회 안내 확인</t>
+          <t>2026-05-04 개장 전 현장 확인</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>교통·대외협력 담당</t>
+          <t>시설·방재 담당</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -6229,17 +5908,17 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>도로관리청/경찰/지자체</t>
+          <t>소방서/베뉴 방재실/시설팀</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>운영본부/안내팀</t>
+          <t>운영본부/구역장</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>도로점용허가증/교통소통대책 승인/통제 공고 캡처</t>
+          <t>가설건축물 신고필증/피난안전 확인서/임시사용 승인 확인</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -6256,17 +5935,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>옥외광고 담당부서/베뉴</t>
+          <t>소방서/베뉴 방재실/안전총괄</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>현수막·배너·안내판·전기 광고물 허가/신고</t>
+          <t>소방·피난 점검표, 화기·위험물 반입 승인, 임시소방시설 확인</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>local_government | venue</t>
+          <t>venue | fire_police_medical | worker_contractor</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -6306,7 +5985,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>광고물 허가·신고필증/베뉴 설치 승인/설치 사진</t>
+          <t>소방·피난 점검표/위험물 반입 승인/개장 전 사진</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -6323,37 +6002,37 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>관할 건축부서/베뉴 시설팀</t>
+          <t>의료담당/AED 관리책임자/119·이송병원</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>가설건축물 축조신고서, 피난안전 확인서, 임시사용승인 확인</t>
+          <t>응급의료·AED·구급 이송 계획, AED 점검·교육·관리서류</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>local_government | venue | fire_police_medical</t>
+          <t>fire_police_medical</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>T-7 설치·작업 전 승인</t>
+          <t>T-1 개장 전 확인</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-05-04 개장 전 현장 확인</t>
+          <t>2026-05-05 운영 중 재점검</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>시설·방재 담당</t>
+          <t>의료담당</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -6363,7 +6042,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>소방서/베뉴 방재실/시설팀</t>
+          <t>119/이송병원/AED 관리책임자</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -6373,7 +6052,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>가설건축물 신고필증/피난안전 확인서/임시사용 승인 확인</t>
+          <t>AED 점검표/응급인력 배치표/119·이송병원 협의 기록</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -6390,17 +6069,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>소방서/베뉴 방재실/안전총괄</t>
+          <t>시공/하역/전기 협력사/안전총괄</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>소방·피난 점검표, 화기·위험물 반입 승인, 임시소방시설 확인</t>
+          <t>설치·철거 작업자 안전계획서, 작업계획서, 교육명단, PPE·작업중지 기준</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>venue | fire_police_medical | worker_contractor</t>
+          <t>venue | worker_contractor</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -6420,7 +6099,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>시설·방재 담당</t>
+          <t>작업책임자</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -6430,7 +6109,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>소방서/베뉴 방재실/시설팀</t>
+          <t>시공/하역/전기 협력사</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -6440,211 +6119,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>소방·피난 점검표/위험물 반입 승인/개장 전 사진</t>
+          <t>작업계획서/교육명단/PPE 지급/작업허가·작업중지 기준</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>개인정보 보호책임자/등록 대행사/보안 담당</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>개인정보 처리방침, 위탁계약, CCTV 안내, 접근권한·접속기록 점검</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>local_government</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>T-14 사전점검</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2026-05-04 고지·권한 최종 확인</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>개인정보보호책임자</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>개인정보보호책임자</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>등록 대행사/보안 담당</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>운영본부</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>처리방침/위탁계약/안내문/CCTV 고지 사진/접속기록 점검표</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>의료담당/AED 관리책임자/119·이송병원</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>응급의료·AED·구급 이송 계획, AED 점검·교육·관리서류</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>fire_police_medical</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>T-1 개장 전 확인</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2026-05-05 운영 중 재점검</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>의료담당</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>안전총괄</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>119/이송병원/AED 관리책임자</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>운영본부/구역장</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>AED 점검표/응급인력 배치표/119·이송병원 협의 기록</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>시공/하역/전기 협력사/안전총괄</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>설치·철거 작업자 안전계획서, 작업계획서, 교육명단, PPE·작업중지 기준</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>venue | worker_contractor</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>T-7 설치·작업 전 승인</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2026-05-04 개장 전 현장 확인</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>작업책임자</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>안전총괄</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>시공/하역/전기 협력사</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>운영본부/구역장</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>작업계획서/교육명단/PPE 지급/작업허가·작업중지 기준</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -6656,7 +6134,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6768,7 +6246,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>도로관리청/교통부서/경찰과 도로점용허가, 교통소통대책, 차로·보도 통제, 원상복구 범위를 확인한다.</t>
+          <t>현재 입력에서는 도로점용·교통통제 조건이 확정되지 않았다.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -6800,7 +6278,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>통행금지·차량 운행 제한이 있으면 공고, 우회도로, 문의처, 비상차량 접근로를 사전 고지한다.</t>
+          <t>외부 대기열, 승하차장, 보행자 흐름, 비상차량 접근로를 현장 확인하고, 도로·보도·광장 점용이나 통행 제한이 확정될 때만 도로점용허가·교통소통대책 제출 액션으로 전환한다.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -6832,7 +6310,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>지자체 옥외행사 안전관리계획과 도로점용/교통소통 조례의 제출기한을 제출 일정·RACI에 반영한다.</t>
+          <t>전환 전에는 관할기관 제출 의무가 아니라 운영본부 확인후보로 관리한다.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -6864,7 +6342,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 서울특별시 송파구 옥외행사의 안전관리에 관한 조례: 천장이 없거나 사방이 폐쇄되지 않은 장소에서 불특정 다수가 참여하는 공연·축제·체육·전시성 행사 / 제출기한 다수 조례에서 행사 5~21일 전 안전관리계획 수립·신고 또는 제출 요구</t>
+          <t>서울특별시 송파구 옥외행사의 안전관리에 관한 조례: 천장이 없거나 사방이 폐쇄되지 않은 장소에서 불특정 다수가 참여하는 공연·축제·체육·전시성 행사 / 제출기한 다수 조례에서 행사 5~21일 전 안전관리계획 수립·신고 또는 제출 요구</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -6896,7 +6374,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 서울특별시 송파구 옥외광고물 등의 관리와 옥외광고산업 진흥에 관한 조례: 행사 홍보·안내를 위해 현수막, 배너, 안내판, 지주형 표시물, 전광류·전기 사용 광고물을 옥외에 표시·설치하는 경우 / 제출기한 표시·설치 전 허가/신고 및 게시대 신청 기한을 관할 지자체 기준으로 확인</t>
+          <t>서울특별시 송파구 옥외광고물 등의 관리와 옥외광고산업 진흥에 관한 조례: 행사 홍보·안내를 위해 현수막, 배너, 안내판, 지주형 표시물, 전광류·전기 사용 광고물을 옥외에 표시·설치하는 경우 / 제출기한 표시·설치 전 허가/신고 및 게시대 신청 기한을 관할 지자체 기준으로 확인</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -6928,7 +6406,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>서울특별시 서울특별시 옥외행사의 안전관리에 관한 조례: 천장이 없거나 사방이 폐쇄되지 않은 장소에서 불특정 다수가 참여하는 공연·축제·체육·전시성 행사 / 제출기한 다수 조례에서 행사 5~21일 전 안전관리계획 수립·신고 또는 제출 요구</t>
+          <t>서울특별시 옥외행사의 안전관리에 관한 조례: 천장이 없거나 사방이 폐쇄되지 않은 장소에서 불특정 다수가 참여하는 공연·축제·체육·전시성 행사 / 제출기한 다수 조례에서 행사 5~21일 전 안전관리계획 수립·신고 또는 제출 요구</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -6960,7 +6438,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 서울특별시 송파구 도로점용공사장 교통소통대책에 관한 조례: 도로·보도·광장 등에 임시시설, 안내물, 부스, 무대, 대기열, 셔틀 승하차장, 행진·퍼레이드, 차량통제 구역을 설치하거나 도로를 점용하는 경우 / 제출기한 도로점용허가 신청 및 교통소통대책 제출 기한은 관할 도로관리청 기준 확인</t>
+          <t>서울특별시 옥외광고물 등의 관리와 옥외광고산업 진흥에 관한 조례: 행사 홍보·안내를 위해 현수막, 배너, 안내판, 지주형 표시물, 전광류·전기 사용 광고물을 옥외에 표시·설치하는 경우 / 제출기한 표시·설치 전 허가/신고 및 게시대 신청 기한을 관할 지자체 기준으로 확인</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -6992,7 +6470,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>서울특별시 송파구 서울특별시 송파구 도로점용료 징수 조례 시행규칙: 도로·보도·광장 등에 임시시설, 안내물, 부스, 무대, 대기열, 셔틀 승하차장, 행진·퍼레이드, 차량통제 구역을 설치하거나 도로를 점용하는 경우 / 제출기한 도로점용허가 신청 및 교통소통대책 제출 기한은 관할 도로관리청 기준 확인</t>
+          <t>교통통제 도면에는 통제구간, 보행자 동선, 차량 우회동선, 비상차량 접근로, 하역/반입 동선, 셔틀·택시·버스 승하차 지점을 한 도면에 표시한다.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -7024,7 +6502,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>서울특별시 서울특별시 옥외광고물 등의 관리와 옥외광고산업 진흥에 관한 조례: 행사 홍보·안내를 위해 현수막, 배너, 안내판, 지주형 표시물, 전광류·전기 사용 광고물을 옥외에 표시·설치하는 경우 / 제출기한 표시·설치 전 허가/신고 및 게시대 신청 기한을 관할 지자체 기준으로 확인</t>
+          <t>보행자 대기열이 차도, 자전거도로, 소방차 진입로, 지하철 출입구, 횡단보도, 버스정류장을 침범하지 않도록 통제선을 설치한다.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -7056,7 +6534,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>도로법 시행령 별표 2: 점용물은 도로 구조 또는 교통에 지장을 주지 않는 위치에 설치</t>
+          <t>야간·우천 조건에서는 조명, 미끄럼, 시야차단, 우산 대기열, 노점/불법주정차 병목을 별도 점검한다.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -7088,7 +6566,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>도로법 시행령 별표 2: 교차·접속·굴곡 부분 점용물 설치 제한 여부 확인</t>
+          <t>개장 전: 통제표지, 라바콘/펜스, 안내요원, 우회 안내판, 무전 채널, 경찰/지자체 연락선을 확인한다.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -7120,7 +6598,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>도로법 시행령 별표 2: 점용물 구조는 무너짐·낙하·벗겨짐·화재·하중 등으로 도로 구조안전 또는 교통에 지장을 주지 않아야 함</t>
+          <t>운영 중: 대기열 길이, 횡단보도 대기, 셔틀·주차장 진입 대기, 응급차 접근 지연, 우회동선 이탈을 30분 간격으로 보고한다.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -7152,7 +6630,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>도로법 시행령 별표 2: 도로 한쪽 통행 유지와 교통 지장 최소화, 1개 차로 이상 차단 시 교통소통대책 수립</t>
+          <t>피크/폐장: 퇴장 분산 방송, 역·버스정류장·주차장 대기열 분리, 승하차장 혼잡 완화, 보행자 역류 방지 기준을 실행한다.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -7184,7 +6662,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>도로법 시행령 별표 2: 공사현장은 울타리 또는 덮개, 야간 적색등·황색등 등 위험방지 조치</t>
+          <t>종료 후: 도로·보도·시설물 원상복구, 통제물 철거, 노면 오염·파손 사진, 민원·사고 기록을 증빙철에 보관한다.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -7216,7 +6694,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>도로법 시행규칙 별지 제11호서식: 행사 설치물이 단순 점용인지 도로공사 시행 허가 대상인지 도로관리청에 확인</t>
+          <t>현수막, 배너, 안내판, 지주형 표시물, 전광류/전기 사용 광고물은 관할 옥외광고 담당부서와 베뉴 설치 승인을 확인한다.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -7248,7 +6726,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>도로법 시행규칙 별지 제11호서식: 공사 위치, 기간, 면적, 구조, 시공방법, 교통처리, 안전시설 계획을 신청 전 정리</t>
+          <t>안내표지는 피난유도등, 소화전, 비상구, 교통표지, 신호등, CCTV, 점자블록을 가리지 않게 설치한다.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -7280,7 +6758,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>도로법 시행규칙 별지 제11호서식: 보행자 우회로, 차로 축소, 야간 설치·철거, 복구계획을 도면과 함께 준비</t>
+          <t>외부 대기열·승하차장·비상차량 접근로 확인 사진</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -7312,7 +6790,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>도로법 시행규칙 별지 제11호서식: 허가 조건을 스태프 브리핑과 일일 안전점검표에 반영</t>
+          <t>도로·보도·광장 점용 없음 또는 조건부 전환 판단 메모</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -7344,7 +6822,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>도로법 시행규칙 별지 제12호서식: 착수일, 공사 구간, 시공자, 현장책임자, 비상연락처를 운영본부와 공유</t>
+          <t>현장 변경 시 관할 도로관리청/경찰 협의 기록</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -7358,934 +6836,6 @@
         </is>
       </c>
       <c r="F22" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>도로·교통</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>도로법 시행규칙 별지 제12호서식: 착수 전 교통안전시설, 보행자 우회 안내, 야간 경광등, 현장 울타리 설치 확인</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>도로·교통</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>도로법 시행규칙 별지 제12호서식: 관람객 운영 시간과 공사·철거 시간이 겹치면 통제구역과 스태프 배치 확정</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>도로·교통</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>도로법 시행규칙 별지 제12호서식: 착수 신고와 베뉴/지자체/경찰 협의 내역을 같은 증빙철에 보관</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>도로·교통</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>도로법 시행규칙 별지 제13호서식: 철거 후 포장, 보도블록, 경계석, 배수, 표지, 차선 등 원상복구 상태 확인</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>도로·교통</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>도로법 시행규칙 별지 제13호서식: 준공검사 전후 사진, 현장 책임자 확인, 도로관리청 보완 지시 이행 기록 보관</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>도로·교통</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>도로법 시행규칙 별지 제13호서식: 행사 종료 뒤 임시시설 잔재와 보행 장애물이 없는지 야간까지 재점검</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>도로·교통</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>도로법 시행규칙 별지 제13호서식: 복구 지연 시 교통안전시설과 보행자 안내를 유지</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>도로·교통</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>도로법 시행규칙 별지 제33호서식: 도로 점용공사 대행 주체와 현장책임자, 보험, 하도급 관계를 확인</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>도로·교통</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>도로법 시행규칙 별지 제33호서식: 대행 통지 범위가 실제 설치·철거·복구 작업 범위와 일치하는지 확인</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>도로·교통</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>도로법 시행규칙 별지 제33호서식: 교통안전시설 설치·유지·철거 책임과 사고 발생 시 보고 책임을 계약서에 명시</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>도로·교통</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>도로법 시행규칙 별지 제33호서식: 대행 통지서와 허가 조건을 운영본부 문서철에 연결</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>도로·교통</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>도로법 시행규칙 별지 제36호서식: 통행 제한 구간, 기간, 제한 대상, 우회도로, 사유, 문의처를 공고·현장안내·온라인 안내에 일치시킴</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>도로·교통</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>도로법 시행규칙 별지 제36호서식: 경찰, 도로관리청, 지자체, 버스·택시·주차 운영자와 우회 동선과 통제 시간을 합의</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>도로·교통</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>도로법 시행규칙 별지 제36호서식: 공고 내용과 현장 표지·입간판·배너 문구가 다른지 개장 전 점검</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>도로·교통</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>도로법 시행규칙 별지 제36호서식: 비상차량 접근 동선과 대피동선은 통행 제한 계획에서 예외로 관리</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>도로·교통</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>교통통제 도면에는 통제구간, 보행자 동선, 차량 우회동선, 비상차량 접근로, 하역/반입 동선, 셔틀·택시·버스 승하차 지점을 한 도면에 표시한다.</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>도로·교통</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>보행자 대기열이 차도, 자전거도로, 소방차 진입로, 지하철 출입구, 횡단보도, 버스정류장을 침범하지 않도록 통제선을 설치한다.</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>도로·교통</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>야간·우천 조건에서는 조명, 미끄럼, 시야차단, 우산 대기열, 노점/불법주정차 병목을 별도 점검한다.</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>도로·교통</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>개장 전: 통제표지, 라바콘/펜스, 안내요원, 우회 안내판, 무전 채널, 경찰/지자체 연락선을 확인한다.</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>도로·교통</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>운영 중: 대기열 길이, 횡단보도 대기, 셔틀·주차장 진입 대기, 응급차 접근 지연, 우회동선 이탈을 30분 간격으로 보고한다.</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>도로·교통</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>피크/폐장: 퇴장 분산 방송, 역·버스정류장·주차장 대기열 분리, 승하차장 혼잡 완화, 보행자 역류 방지 기준을 실행한다.</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>도로·교통</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>종료 후: 도로·보도·시설물 원상복구, 통제물 철거, 노면 오염·파손 사진, 민원·사고 기록을 증빙철에 보관한다.</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>도로·교통</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>현수막, 배너, 안내판, 지주형 표시물, 전광류/전기 사용 광고물은 관할 옥외광고 담당부서와 베뉴 설치 승인을 확인한다.</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>도로·교통</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>안내표지는 피난유도등, 소화전, 비상구, 교통표지, 신호등, CCTV, 점자블록을 가리지 않게 설치한다.</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>도로·교통</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>도로점용허가증 또는 협의 회신</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>도로·교통</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>교통소통대책/통제 도면</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>도로·교통</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>통행금지·차량 운행 제한 공고 또는 안내 캡처</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>도로·교통</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>경찰·도로관리청·지자체 협의 메모</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>도로·교통</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>현장 설치 전/후 사진과 원상복구 확인 사진</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
         <is>
           <t/>
         </is>

--- a/outputs/may-2026-real-events/details/03-hangang-drone-light-show-2026/bundle/tables/safety-checklists.xlsx
+++ b/outputs/may-2026-real-events/details/03-hangang-drone-light-show-2026/bundle/tables/safety-checklists.xlsx
@@ -2796,7 +2796,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2918,27 +2918,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>옥외광고 담당부서/베뉴</t>
+          <t>관할 건축부서/베뉴 시설팀</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>현수막·배너·안내판·전기 광고물 허가/신고</t>
+          <t>가설건축물 축조신고서, 피난안전 확인서, 임시사용승인 확인</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>옥외 임시 안내물, 지주형 표시물, 전광류 또는 전기 사용 광고물을 설치하는 경우</t>
+          <t>대형 텐트, 임시 전시장, 복층/다층 임시구조물, 공사 중 구역 임시 사용</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>표시·설치 전</t>
+          <t>설치 전 신고·승인, 개장 전 피난안전 확인</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>옥외광고물법 시행령 제5·7·12·14조와 관할 조례 확인</t>
+          <t>건축법 시행규칙 별지 제8·8의2·17호서식</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -2955,27 +2955,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>관할 건축부서/베뉴 시설팀</t>
+          <t>소방서/베뉴 방재실/안전총괄</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>가설건축물 축조신고서, 피난안전 확인서, 임시사용승인 확인</t>
+          <t>소방·피난 점검표, 화기·위험물 반입 승인, 임시소방시설 확인</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>대형 텐트, 임시 전시장, 복층/다층 임시구조물, 공사 중 구역 임시 사용</t>
+          <t>화기, 위험물, 임시전기, 부스·무대 설치, 피난통로 차단 위험이 있는 경우</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>설치 전 신고·승인, 개장 전 피난안전 확인</t>
+          <t>설치 전, 개장 전, 피크 전, 철거 전</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>건축법 시행규칙 별지 제8·8의2·17호서식</t>
+          <t>화재예방법·소방시설법 하위 별표와 베뉴 방재실 승인조건</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2992,27 +2992,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>소방서/베뉴 방재실/안전총괄</t>
+          <t>의료담당/AED 관리책임자/119·이송병원</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>소방·피난 점검표, 화기·위험물 반입 승인, 임시소방시설 확인</t>
+          <t>응급의료·AED·구급 이송 계획, AED 점검·교육·관리서류</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>화기, 위험물, 임시전기, 부스·무대 설치, 피난통로 차단 위험이 있는 경우</t>
+          <t>대규모 인파, 고령자/영유아/장애인, 스탠딩 공연, 야외·폭염·야간 행사</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>설치 전, 개장 전, 피크 전, 철거 전</t>
+          <t>개장 전, 운영 중, 사용/이송 발생 시</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>화재예방법·소방시설법 하위 별표와 베뉴 방재실 승인조건</t>
+          <t>응급의료법 AED 설치·관리, 시행규칙 구급차 장비·운행기록 기준</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -3029,67 +3029,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>의료담당/AED 관리책임자/119·이송병원</t>
+          <t>시공/하역/전기 협력사/안전총괄</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>응급의료·AED·구급 이송 계획, AED 점검·교육·관리서류</t>
+          <t>설치·철거 작업자 안전계획서, 작업계획서, 교육명단, PPE·작업중지 기준</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>대규모 인파, 고령자/영유아/장애인, 스탠딩 공연, 야외·폭염·야간 행사</t>
+          <t>부스·무대·트러스·전기·고소·중량물·화기·철거 작업이 있는 경우</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>개장 전, 운영 중, 사용/이송 발생 시</t>
+          <t>작업 전, 작업 중 변경 시, 철거 전</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>응급의료법 AED 설치·관리, 시행규칙 구급차 장비·운행기록 기준</t>
+          <t>산안법, 산안기준규칙 제38·42·321조, KOSHA Guide worker-safety layer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>시공/하역/전기 협력사/안전총괄</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>설치·철거 작업자 안전계획서, 작업계획서, 교육명단, PPE·작업중지 기준</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>부스·무대·트러스·전기·고소·중량물·화기·철거 작업이 있는 경우</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>작업 전, 작업 중 변경 시, 철거 전</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>산안법, 산안기준규칙 제38·42·321조, KOSHA Guide worker-safety layer</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
         <is>
           <t>open</t>
         </is>
@@ -4990,7 +4953,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>730</t>
         </is>
       </c>
     </row>
@@ -5589,7 +5552,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5697,7 +5660,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>작업책임자</t>
+          <t>공연안전 담당</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -5707,17 +5670,17 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>시공/하역/전기 협력사</t>
+          <t>공연/문화 담당부서·베뉴 기술지원</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>운영본부/구역장</t>
+          <t>운영본부/무대감독/보안·의료팀</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>작업계획서/교육명단/PPE 지급/작업허가·작업중지 기준</t>
+          <t>공연 재해대처계획/안전교육 명단/무대·리깅 승인/공연중지 기준</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -5801,17 +5764,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>옥외광고 담당부서/베뉴</t>
+          <t>관할 건축부서/베뉴 시설팀</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>현수막·배너·안내판·전기 광고물 허가/신고</t>
+          <t>가설건축물 축조신고서, 피난안전 확인서, 임시사용승인 확인</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>local_government | venue</t>
+          <t>local_government | venue | fire_police_medical</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -5851,7 +5814,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>광고물 허가·신고필증/베뉴 설치 승인/설치 사진</t>
+          <t>가설건축물 신고필증/피난안전 확인서/임시사용 승인 확인</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -5868,17 +5831,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>관할 건축부서/베뉴 시설팀</t>
+          <t>소방서/베뉴 방재실/안전총괄</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>가설건축물 축조신고서, 피난안전 확인서, 임시사용승인 확인</t>
+          <t>소방·피난 점검표, 화기·위험물 반입 승인, 임시소방시설 확인</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>local_government | venue | fire_police_medical</t>
+          <t>venue | fire_police_medical | worker_contractor</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -5918,7 +5881,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>가설건축물 신고필증/피난안전 확인서/임시사용 승인 확인</t>
+          <t>소방·피난 점검표/위험물 반입 승인/개장 전 사진</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -5935,37 +5898,37 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>소방서/베뉴 방재실/안전총괄</t>
+          <t>의료담당/AED 관리책임자/119·이송병원</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>소방·피난 점검표, 화기·위험물 반입 승인, 임시소방시설 확인</t>
+          <t>응급의료·AED·구급 이송 계획, AED 점검·교육·관리서류</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>venue | fire_police_medical | worker_contractor</t>
+          <t>fire_police_medical</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>T-7 설치·작업 전 승인</t>
+          <t>T-1 개장 전 확인</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-05-04 개장 전 현장 확인</t>
+          <t>2026-05-05 운영 중 재점검</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>시설·방재 담당</t>
+          <t>의료담당</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -5975,7 +5938,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>소방서/베뉴 방재실/시설팀</t>
+          <t>119/이송병원/AED 관리책임자</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -5985,7 +5948,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>소방·피난 점검표/위험물 반입 승인/개장 전 사진</t>
+          <t>AED 점검표/응급인력 배치표/119·이송병원 협의 기록</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -6002,37 +5965,37 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>의료담당/AED 관리책임자/119·이송병원</t>
+          <t>시공/하역/전기 협력사/안전총괄</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>응급의료·AED·구급 이송 계획, AED 점검·교육·관리서류</t>
+          <t>설치·철거 작업자 안전계획서, 작업계획서, 교육명단, PPE·작업중지 기준</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>fire_police_medical</t>
+          <t>venue | worker_contractor</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>T-1 개장 전 확인</t>
+          <t>T-7 설치·작업 전 승인</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-05-05 운영 중 재점검</t>
+          <t>2026-05-04 개장 전 현장 확인</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>의료담당</t>
+          <t>작업책임자</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -6042,7 +6005,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>119/이송병원/AED 관리책임자</t>
+          <t>시공/하역/전기 협력사</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -6052,77 +6015,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>AED 점검표/응급인력 배치표/119·이송병원 협의 기록</t>
+          <t>작업계획서/교육명단/PPE 지급/작업허가·작업중지 기준</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>시공/하역/전기 협력사/안전총괄</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>설치·철거 작업자 안전계획서, 작업계획서, 교육명단, PPE·작업중지 기준</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>venue | worker_contractor</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>T-7 설치·작업 전 승인</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2026-05-04 개장 전 현장 확인</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>작업책임자</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>안전총괄</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>시공/하역/전기 협력사</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>운영본부/구역장</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>작업계획서/교육명단/PPE 지급/작업허가·작업중지 기준</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
         <is>
           <t>open</t>
         </is>
